--- a/artfynd/A 61199-2023 artfynd.xlsx
+++ b/artfynd/A 61199-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61199-2023 artfynd.xlsx
+++ b/artfynd/A 61199-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>83572305</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401272.5990392926</v>
+        <v>401273</v>
       </c>
       <c r="R2" t="n">
-        <v>6419825.749057868</v>
+        <v>6419826</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,19 +752,9 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83572464</v>
+        <v>83572352</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401261.5707669839</v>
+        <v>401347</v>
       </c>
       <c r="R3" t="n">
-        <v>6419853.661023518</v>
+        <v>6419871</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +859,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>BF5FEBBA-9007-4D20-8476-B1FCE4BC7C1B</t>
+          <t>A924A93B-A63C-4135-841A-40A93774DB10</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -887,24 +867,14 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>{BC9D917E-F476-4736-85B0-F60A76EE0015}</t>
+          <t>{6773CD9E-819D-44C7-9C2E-33FB096901C0}</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83572481</v>
+        <v>83572425</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401259.5727852639</v>
+        <v>401265</v>
       </c>
       <c r="R4" t="n">
-        <v>6419859.025663917</v>
+        <v>6419851</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1009,7 +974,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>85519702-75DD-4C0A-8857-F5696984D64D</t>
+          <t>6725A917-34AE-42F0-B929-AEA33CD5C621</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1017,24 +982,14 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>{CA0BA5B4-91A4-4F6B-B3BA-8F6E330B009E}</t>
+          <t>{9C7AF405-DFA8-4B5A-ABCE-02F1BC73DC70}</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83572425</v>
+        <v>83572432</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401264.6986723802</v>
+        <v>401305</v>
       </c>
       <c r="R5" t="n">
-        <v>6419850.926231966</v>
+        <v>6419862</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1139,7 +1089,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>6725A917-34AE-42F0-B929-AEA33CD5C621</t>
+          <t>48037B21-7A76-4414-AE56-6847753C2486</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1147,24 +1097,14 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>{9C7AF405-DFA8-4B5A-ABCE-02F1BC73DC70}</t>
+          <t>{A391BB88-12F0-4C08-9982-B2F49A0BD50E}</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,15 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83572432</v>
+        <v>83572464</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401305.4490098737</v>
+        <v>401262</v>
       </c>
       <c r="R6" t="n">
-        <v>6419862.147523582</v>
+        <v>6419854</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1269,7 +1204,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>48037B21-7A76-4414-AE56-6847753C2486</t>
+          <t>BF5FEBBA-9007-4D20-8476-B1FCE4BC7C1B</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1277,24 +1212,14 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>{A391BB88-12F0-4C08-9982-B2F49A0BD50E}</t>
+          <t>{BC9D917E-F476-4736-85B0-F60A76EE0015}</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,15 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83572539</v>
+        <v>83572476</v>
       </c>
       <c r="B7" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>401280.0110091943</v>
+        <v>401217</v>
       </c>
       <c r="R7" t="n">
-        <v>6419823.971776703</v>
+        <v>6419854</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1399,7 +1319,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>B58BB394-6C85-4ACC-9640-AD5AA3798BA0</t>
+          <t>CD46C3E4-EDC1-4A10-A2C7-1B2B10198F5F</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1407,24 +1327,14 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>{F9E5B86C-FE86-472B-B487-0691F1D2A6FA}</t>
+          <t>{C57E5129-7DDB-48D1-9B74-5C7A16A7F7FA}</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,6 +1358,236 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>83572481</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>401260</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6419859</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällstad</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>85519702-75DD-4C0A-8857-F5696984D64D</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2011-06-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2011-06-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>{CA0BA5B4-91A4-4F6B-B3BA-8F6E330B009E}</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>83572539</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>401280</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6419824</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällstad</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>B58BB394-6C85-4ACC-9640-AD5AA3798BA0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2011-06-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2011-06-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>{F9E5B86C-FE86-472B-B487-0691F1D2A6FA}</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/A 61199-2023 artfynd.xlsx
+++ b/artfynd/A 61199-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572305</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572352</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572425</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572432</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572464</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572476</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572481</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,8 +1632,23 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83572539</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>